--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,271 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123324625</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98282</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långbroarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>605014</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6727046</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2024_994</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123324626</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98282</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långbroarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>605076</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6726895</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_993</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 25 m öst om hyggeskant</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,7 +806,7 @@
         <v>123324625</v>
       </c>
       <c r="B3" t="n">
-        <v>98282</v>
+        <v>98285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>123324626</v>
       </c>
       <c r="B4" t="n">
-        <v>98282</v>
+        <v>98285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1061,6 +1061,396 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123421114</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91400</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långbroarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>605398</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6726563</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_3195</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Isaksson, Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123421115</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91242</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>658</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långbroarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>605411</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6726702</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2024_3194</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>David Isaksson, Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123421110</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98285</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långbroarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>605332</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6726660</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2024_3199</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324625</v>
+        <v>123324626</v>
       </c>
       <c r="B3" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605014</v>
+        <v>605076</v>
       </c>
       <c r="R3" t="n">
-        <v>6727046</v>
+        <v>6726895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_994</t>
+          <t>2024_993</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca 25 m öst om hyggeskant</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324626</v>
+        <v>123324625</v>
       </c>
       <c r="B4" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,7 +973,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605076</v>
+        <v>605014</v>
       </c>
       <c r="R4" t="n">
-        <v>6726895</v>
+        <v>6727046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1017,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_993</t>
+          <t>2024_994</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1022,7 +1027,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,12 +1037,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 25 m öst om hyggeskant</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1071,7 @@
         <v>123421114</v>
       </c>
       <c r="B5" t="n">
-        <v>91400</v>
+        <v>91402</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>123421115</v>
       </c>
       <c r="B6" t="n">
-        <v>91242</v>
+        <v>91244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>123421110</v>
       </c>
       <c r="B7" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324626</v>
+        <v>123324625</v>
       </c>
       <c r="B3" t="n">
-        <v>98287</v>
+        <v>98293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605076</v>
+        <v>605014</v>
       </c>
       <c r="R3" t="n">
-        <v>6726895</v>
+        <v>6727046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_993</t>
+          <t>2024_994</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca 25 m öst om hyggeskant</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324625</v>
+        <v>123324626</v>
       </c>
       <c r="B4" t="n">
-        <v>98287</v>
+        <v>98293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -973,7 +968,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605014</v>
+        <v>605076</v>
       </c>
       <c r="R4" t="n">
-        <v>6727046</v>
+        <v>6726895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1012,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_994</t>
+          <t>2024_993</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1027,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1037,7 +1032,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 25 m öst om hyggeskant</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123421114</v>
+        <v>123421115</v>
       </c>
       <c r="B5" t="n">
-        <v>91402</v>
+        <v>91250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,35 +1080,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605398</v>
+        <v>605411</v>
       </c>
       <c r="R5" t="n">
-        <v>6726563</v>
+        <v>6726702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_3195</t>
+          <t>2024_3194</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1198,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123421115</v>
+        <v>123421110</v>
       </c>
       <c r="B6" t="n">
-        <v>91244</v>
+        <v>98293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,35 +1210,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605411</v>
+        <v>605332</v>
       </c>
       <c r="R6" t="n">
-        <v>6726702</v>
+        <v>6726660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_3194</t>
+          <t>2024_3199</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson, Linnéa Kjellberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123421110</v>
+        <v>123421114</v>
       </c>
       <c r="B7" t="n">
-        <v>98287</v>
+        <v>91408</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,25 +1340,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605332</v>
+        <v>605398</v>
       </c>
       <c r="R7" t="n">
-        <v>6726660</v>
+        <v>6726563</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_3199</t>
+          <t>2024_3195</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Linnéa Kjellberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>123324625</v>
       </c>
       <c r="B3" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>123324626</v>
       </c>
       <c r="B4" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>123421115</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>91253</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, David Isaksson</t>
+          <t>David Isaksson, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1198,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123421110</v>
+        <v>123421114</v>
       </c>
       <c r="B6" t="n">
-        <v>98293</v>
+        <v>91411</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,25 +1210,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605332</v>
+        <v>605398</v>
       </c>
       <c r="R6" t="n">
-        <v>6726660</v>
+        <v>6726563</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_3199</t>
+          <t>2024_3195</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123421114</v>
+        <v>123421110</v>
       </c>
       <c r="B7" t="n">
-        <v>91408</v>
+        <v>98296</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,25 +1340,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605398</v>
+        <v>605332</v>
       </c>
       <c r="R7" t="n">
-        <v>6726563</v>
+        <v>6726660</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_3195</t>
+          <t>2024_3199</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, David Isaksson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>123324625</v>
       </c>
       <c r="B3" t="n">
-        <v>98296</v>
+        <v>98313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>123324626</v>
       </c>
       <c r="B4" t="n">
-        <v>98296</v>
+        <v>98313</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123421115</v>
+        <v>123421110</v>
       </c>
       <c r="B5" t="n">
-        <v>91253</v>
+        <v>98313</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,35 +1080,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605411</v>
+        <v>605332</v>
       </c>
       <c r="R5" t="n">
-        <v>6726702</v>
+        <v>6726660</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_3194</t>
+          <t>2024_3199</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson, Linnéa Kjellberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1201,7 +1201,7 @@
         <v>123421114</v>
       </c>
       <c r="B6" t="n">
-        <v>91411</v>
+        <v>91428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123421110</v>
+        <v>123421115</v>
       </c>
       <c r="B7" t="n">
-        <v>98296</v>
+        <v>91270</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,35 +1340,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605332</v>
+        <v>605411</v>
       </c>
       <c r="R7" t="n">
-        <v>6726660</v>
+        <v>6726702</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_3199</t>
+          <t>2024_3194</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>123324625</v>
       </c>
       <c r="B3" t="n">
-        <v>98313</v>
+        <v>98419</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>123324626</v>
       </c>
       <c r="B4" t="n">
-        <v>98313</v>
+        <v>98419</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>123421110</v>
       </c>
       <c r="B5" t="n">
-        <v>98313</v>
+        <v>98419</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123421114</v>
+        <v>123421115</v>
       </c>
       <c r="B6" t="n">
-        <v>91428</v>
+        <v>91275</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,35 +1210,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605398</v>
+        <v>605411</v>
       </c>
       <c r="R6" t="n">
-        <v>6726563</v>
+        <v>6726702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_3195</t>
+          <t>2024_3194</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123421115</v>
+        <v>123421114</v>
       </c>
       <c r="B7" t="n">
-        <v>91270</v>
+        <v>91433</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,35 +1340,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605411</v>
+        <v>605398</v>
       </c>
       <c r="R7" t="n">
-        <v>6726702</v>
+        <v>6726563</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_3194</t>
+          <t>2024_3195</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324625</v>
+        <v>123324626</v>
       </c>
       <c r="B3" t="n">
-        <v>98419</v>
+        <v>98421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605014</v>
+        <v>605076</v>
       </c>
       <c r="R3" t="n">
-        <v>6727046</v>
+        <v>6726895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_994</t>
+          <t>2024_993</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca 25 m öst om hyggeskant</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324626</v>
+        <v>123324625</v>
       </c>
       <c r="B4" t="n">
-        <v>98419</v>
+        <v>98421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,7 +973,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605076</v>
+        <v>605014</v>
       </c>
       <c r="R4" t="n">
-        <v>6726895</v>
+        <v>6727046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1017,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_993</t>
+          <t>2024_994</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1022,7 +1027,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,12 +1037,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 25 m öst om hyggeskant</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123421110</v>
+        <v>123421114</v>
       </c>
       <c r="B5" t="n">
-        <v>98419</v>
+        <v>91435</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,25 +1080,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605332</v>
+        <v>605398</v>
       </c>
       <c r="R5" t="n">
-        <v>6726660</v>
+        <v>6726563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_3199</t>
+          <t>2024_3195</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1201,7 +1201,7 @@
         <v>123421115</v>
       </c>
       <c r="B6" t="n">
-        <v>91275</v>
+        <v>91277</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123421114</v>
+        <v>123421110</v>
       </c>
       <c r="B7" t="n">
-        <v>91433</v>
+        <v>98421</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,25 +1340,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605398</v>
+        <v>605332</v>
       </c>
       <c r="R7" t="n">
-        <v>6726563</v>
+        <v>6726660</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_3195</t>
+          <t>2024_3199</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson, Linnéa Kjellberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324626</v>
+        <v>123324625</v>
       </c>
       <c r="B3" t="n">
-        <v>98421</v>
+        <v>97996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605076</v>
+        <v>605014</v>
       </c>
       <c r="R3" t="n">
-        <v>6726895</v>
+        <v>6727046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_993</t>
+          <t>2024_994</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca 25 m öst om hyggeskant</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324625</v>
+        <v>123324626</v>
       </c>
       <c r="B4" t="n">
-        <v>98421</v>
+        <v>97996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -973,7 +968,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605014</v>
+        <v>605076</v>
       </c>
       <c r="R4" t="n">
-        <v>6727046</v>
+        <v>6726895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1012,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_994</t>
+          <t>2024_993</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1027,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1037,7 +1032,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 25 m öst om hyggeskant</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123421114</v>
+        <v>123421115</v>
       </c>
       <c r="B5" t="n">
-        <v>91435</v>
+        <v>91277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,35 +1080,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605398</v>
+        <v>605411</v>
       </c>
       <c r="R5" t="n">
-        <v>6726563</v>
+        <v>6726702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_3195</t>
+          <t>2024_3194</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123421115</v>
+        <v>123421110</v>
       </c>
       <c r="B6" t="n">
-        <v>91277</v>
+        <v>97996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,35 +1210,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605411</v>
+        <v>605332</v>
       </c>
       <c r="R6" t="n">
-        <v>6726702</v>
+        <v>6726660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_3194</t>
+          <t>2024_3199</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson, Linnéa Kjellberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123421110</v>
+        <v>123421114</v>
       </c>
       <c r="B7" t="n">
-        <v>98421</v>
+        <v>91435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,25 +1340,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605332</v>
+        <v>605398</v>
       </c>
       <c r="R7" t="n">
-        <v>6726660</v>
+        <v>6726563</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_3199</t>
+          <t>2024_3195</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324625</v>
+        <v>123324626</v>
       </c>
       <c r="B3" t="n">
         <v>97996</v>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605014</v>
+        <v>605076</v>
       </c>
       <c r="R3" t="n">
-        <v>6727046</v>
+        <v>6726895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_994</t>
+          <t>2024_993</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca 25 m öst om hyggeskant</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,7 +938,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324626</v>
+        <v>123324625</v>
       </c>
       <c r="B4" t="n">
         <v>97996</v>
@@ -968,7 +973,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605076</v>
+        <v>605014</v>
       </c>
       <c r="R4" t="n">
-        <v>6726895</v>
+        <v>6727046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1017,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_993</t>
+          <t>2024_994</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1022,7 +1027,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,12 +1037,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 25 m öst om hyggeskant</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123421115</v>
+        <v>123421114</v>
       </c>
       <c r="B5" t="n">
-        <v>91277</v>
+        <v>91435</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,35 +1080,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605411</v>
+        <v>605398</v>
       </c>
       <c r="R5" t="n">
-        <v>6726702</v>
+        <v>6726563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_3194</t>
+          <t>2024_3195</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123421110</v>
+        <v>123421115</v>
       </c>
       <c r="B6" t="n">
-        <v>97996</v>
+        <v>91277</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,35 +1210,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605332</v>
+        <v>605411</v>
       </c>
       <c r="R6" t="n">
-        <v>6726660</v>
+        <v>6726702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_3199</t>
+          <t>2024_3194</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123421114</v>
+        <v>123421110</v>
       </c>
       <c r="B7" t="n">
-        <v>91435</v>
+        <v>97996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,25 +1340,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605398</v>
+        <v>605332</v>
       </c>
       <c r="R7" t="n">
-        <v>6726563</v>
+        <v>6726660</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_3195</t>
+          <t>2024_3199</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson, Linnéa Kjellberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -1068,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123421114</v>
+        <v>123421115</v>
       </c>
       <c r="B5" t="n">
-        <v>91435</v>
+        <v>91277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,35 +1080,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605398</v>
+        <v>605411</v>
       </c>
       <c r="R5" t="n">
-        <v>6726563</v>
+        <v>6726702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_3195</t>
+          <t>2024_3194</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123421115</v>
+        <v>123421110</v>
       </c>
       <c r="B6" t="n">
-        <v>91277</v>
+        <v>97996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,35 +1210,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605411</v>
+        <v>605332</v>
       </c>
       <c r="R6" t="n">
-        <v>6726702</v>
+        <v>6726660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_3194</t>
+          <t>2024_3199</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson, Linnéa Kjellberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123421110</v>
+        <v>123421114</v>
       </c>
       <c r="B7" t="n">
-        <v>97996</v>
+        <v>91435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,25 +1340,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605332</v>
+        <v>605398</v>
       </c>
       <c r="R7" t="n">
-        <v>6726660</v>
+        <v>6726563</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_3199</t>
+          <t>2024_3195</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324626</v>
+        <v>123324625</v>
       </c>
       <c r="B3" t="n">
         <v>97996</v>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605076</v>
+        <v>605014</v>
       </c>
       <c r="R3" t="n">
-        <v>6726895</v>
+        <v>6727046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_993</t>
+          <t>2024_994</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca 25 m öst om hyggeskant</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,7 +933,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324625</v>
+        <v>123324626</v>
       </c>
       <c r="B4" t="n">
         <v>97996</v>
@@ -973,7 +968,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605014</v>
+        <v>605076</v>
       </c>
       <c r="R4" t="n">
-        <v>6727046</v>
+        <v>6726895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1012,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_994</t>
+          <t>2024_993</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1027,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1037,7 +1032,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 25 m öst om hyggeskant</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,6 +1456,121 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130669564</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57033</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Forsbacka, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>604988</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6727108</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -1461,7 +1461,7 @@
         <v>130669564</v>
       </c>
       <c r="B8" t="n">
-        <v>57033</v>
+        <v>57035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -1461,7 +1461,7 @@
         <v>130669564</v>
       </c>
       <c r="B8" t="n">
-        <v>57035</v>
+        <v>57043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -1461,7 +1461,7 @@
         <v>130669564</v>
       </c>
       <c r="B8" t="n">
-        <v>57043</v>
+        <v>57044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118003169</v>
+        <v>123421115</v>
       </c>
       <c r="B2" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,31 +708,24 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västbyggeby fäbodar, Gstr</t>
+          <t>Långbroarna, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604942</v>
+        <v>605411</v>
       </c>
       <c r="R2" t="n">
-        <v>6727121</v>
+        <v>6726702</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,24 +747,29 @@
           <t>Valbo</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2024_3194</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>04:20</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>04:20</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,59 +784,58 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>David Isaksson, Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324625</v>
+        <v>123421113</v>
       </c>
       <c r="B3" t="n">
-        <v>97996</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -852,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605014</v>
+        <v>605385</v>
       </c>
       <c r="R3" t="n">
-        <v>6727046</v>
+        <v>6726557</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,27 +874,32 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_994</t>
+          <t>2024_3196</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På klenare granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -933,47 +930,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324626</v>
+        <v>123421114</v>
       </c>
       <c r="B4" t="n">
-        <v>97996</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605076</v>
+        <v>605398</v>
       </c>
       <c r="R4" t="n">
-        <v>6726895</v>
+        <v>6726563</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,32 +1004,27 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_993</t>
+          <t>2024_3195</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 25 m öst om hyggeskant</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1057,7 +1044,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>David Isaksson, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1068,15 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123421110</v>
+        <v>123324627</v>
       </c>
       <c r="B5" t="n">
-        <v>98018</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1106,21 +1088,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långbroarna, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605332</v>
+        <v>605219</v>
       </c>
       <c r="R5" t="n">
-        <v>6726660</v>
+        <v>6727042</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,27 +1124,32 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_3199</t>
+          <t>2024_992</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hackspår på död stående tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1198,37 +1180,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123421114</v>
+        <v>123421116</v>
       </c>
       <c r="B6" t="n">
-        <v>91457</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1236,9 +1213,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1247,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605398</v>
+        <v>605455</v>
       </c>
       <c r="R6" t="n">
-        <v>6726563</v>
+        <v>6726766</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,7 +1254,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_3195</t>
+          <t>2024_3193</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1287,7 +1264,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1297,7 +1274,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1294,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1328,62 +1305,64 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123421115</v>
+        <v>118003168</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långbroarna, Gstr</t>
+          <t>Västbyggeby fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605411</v>
+        <v>604942</v>
       </c>
       <c r="R7" t="n">
-        <v>6726702</v>
+        <v>6727121</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1405,29 +1384,24 @@
           <t>Valbo</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2024_3194</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>04:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>04:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,30 +1416,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson, Linnéa Kjellberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>130669564</v>
       </c>
       <c r="B8" t="n">
-        <v>57064</v>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1566,6 +1536,386 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123324625</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långbroarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>605014</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6727046</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2024_994</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123324626</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långbroarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>605076</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6726895</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2024_993</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ca 25 m öst om hyggeskant</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123421110</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långbroarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>605332</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6726660</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2024_3199</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 48800-2024 artfynd.xlsx
+++ b/artfynd/A 48800-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421115</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421113</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421114</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1177,6 +1197,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324627</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421116</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1425,6 +1455,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118003168</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1540,6 +1575,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669564</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1665,6 +1705,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324625</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1795,6 +1840,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324626</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1920,8 +1970,25 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421110</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>